--- a/stories/arbres/ATOM-TMP.MET.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo veut sortir avec maman. Il fait froid. Maman prend le manteau. Kenzo enfile le manteau. Dehors, il y a de la pluie. Maman prend les bottes. Kenzo met les bottes. Ses pieds sont au sec. Maman ouvre la porte. Kenzo donne la main. Ils marchent. Maman dit : froid, le manteau. Pluie, les bottes.</t>
+          <t>Kenzo veut sortir avec maman. Il fait froid. Maman prend le manteau. Kenzo enfile le manteau. Dehors, il y a de la pluie. Maman prend les bottes. Kenzo met les bottes. Ses pieds sont au sec. Maman ouvre la porte. Kenzo donne la main. Ils marchent. Froid, le manteau. Pluie, les bottes.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,12 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo veut sortir avec maman. Il fait froid. Maman prend le manteau. Kenzo enfile le manteau. Dehors, il y a de la pluie. Maman prend les bottes. Kenzo met les bottes. Ses pieds sont au sec. Maman ouvre la porte. Kenzo donne la main. Ils marchent.
+maman|Froid, le manteau. Pluie, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1487,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Il pleut. Que met Kenzo ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1656,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a mis le manteau. Il a mis les bottes. Maman était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1823,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo entend la pluie. Ses pieds restent au sec.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1990,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2030,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MET.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1311,6 +1316,7 @@
 maman|Froid, le manteau. Pluie, les bottes.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1494,6 +1500,7 @@
           <t>narrateur|Il pleut. Que met Kenzo ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1661,6 +1668,7 @@
           <t>narrateur|Kenzo a mis le manteau. Il a mis les bottes. Maman était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1828,6 +1836,7 @@
           <t>narrateur|Kenzo entend la pluie. Ses pieds restent au sec.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1995,6 +2004,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2013,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2037,6 +2047,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2238,6 +2262,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.MET.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le manteau de Kenzo</t>
+          <t>La flaque du jardin</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut la flaque du jardin. Il pleut. Une botte est à l'envers. Elles la retournent. Mila pose un pied. Ploc.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo veut sortir avec maman. Il fait froid. Maman prend le manteau. Kenzo enfile le manteau. Dehors, il y a de la pluie. Maman prend les bottes. Kenzo met les bottes. Ses pieds sont au sec. Maman ouvre la porte. Kenzo donne la main. Ils marchent. Froid, le manteau. Pluie, les bottes.</t>
+          <t>Sur la vitre, les gouttes courent très vite. Le cerisier du jardin penche sous l'eau. Une flaque ronde attend près du bac. Mila vit ici, avec maman. La maison sent le cacao tiède. Deux tasses attendent sur la table. Le paillasson est déjà mouillé. Une feuille collée y brille. Tu as vu la flaque ? Oui, maman. Je veux aller dedans. Il pleut fort, tu entends ? En ce moment, Mila va vers la porte. La pluie tape le bois. Maman tend le manteau bleu. Mila glisse les bras dedans. Le tissu est un peu froid. Puis il réchauffe les épaules. Mes bottes. Une botte est à l'envers. La semelle regarde le plafond. Elle est drôle. On la retourne ensemble ? Mila tire la botte. Maman aide un peu. La botte redevient une botte. L'autre maintenant. L'autre botte est déjà droite. Mila enfile les deux. Ses pieds sont au chaud. Prête pour la flaque ? Oui ! Elles ouvrent la porte. L'air sent la terre mouillée. La flaque brille comme un miroir. Mila pose un pied. Ploc. Puis l'autre pied. L'eau saute sur le manteau. Elle est froide ! Tes pieds restent au sec ? Oui, maman. Merci. Tu as retourné la botte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Kenzo veut sortir avec maman. Il fait &lt;emphasis level="moderate"&gt;froid&lt;/emphasis&gt;. Maman prend le manteau. Kenzo enfile le manteau. Dehors, il y a de la pluie. Maman prend les bottes. Kenzo met les bottes. Ses pieds sont au sec. Maman ouvre la porte. Kenzo donne la main. Ils marchent. Maman dit : froid, le manteau. Pluie, les bottes.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur la vitre, les gouttes courent très vite. Le cerisier du jardin penche sous l'eau. Une flaque ronde attend près du bac. Mila vit ici, avec maman. La maison sent le cacao tiède. Deux tasses attendent sur la table. Le paillasson est déjà mouillé. Une feuille collée y brille. Tu as vu la flaque ? Oui, maman. Je veux aller dedans. Il pleut fort, tu entends ? En ce moment, Mila va vers la porte. La pluie tape le bois. Maman tend le manteau bleu. Mila glisse les bras dedans. Le tissu est un peu froid. Puis il réchauffe les épaules. Mes bottes. Une botte est à l'envers. La semelle regarde le plafond. Elle est drôle. On la retourne ensemble ? Mila tire la botte. Maman aide un peu. La botte redevient une botte. L'autre maintenant. L'autre botte est déjà droite. Mila enfile les deux. Ses pieds sont au chaud. Prête pour la flaque ? Oui ! Elles ouvrent la porte. L'air sent la terre mouillée. La flaque brille comme un miroir. Mila pose un pied. Ploc. Puis l'autre pied. L'eau saute sur le manteau. Elle est froide ! Tes pieds restent au sec ? Oui, maman. Merci. Tu as retourné la botte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,11 +1324,52 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo veut sortir avec maman. Il fait froid. Maman prend le manteau. Kenzo enfile le manteau. Dehors, il y a de la pluie. Maman prend les bottes. Kenzo met les bottes. Ses pieds sont au sec. Maman ouvre la porte. Kenzo donne la main. Ils marchent.
-maman|Froid, le manteau. Pluie, les bottes.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Sur la vitre, les gouttes courent très vite.
+narrateur|Le cerisier du jardin penche sous l'eau.
+narrateur|Une flaque ronde attend près du bac.
+narrateur|Mila vit ici, avec maman.
+narrateur|La maison sent le cacao tiède.
+narrateur|Deux tasses attendent sur la table.
+narrateur|Le paillasson est déjà mouillé.
+narrateur|Une feuille collée y brille.
+maman|Tu as vu la flaque ?
+enfant-f|Oui, maman.
+enfant-f|Je veux aller dedans.
+maman|Il pleut fort, tu entends ?
+narrateur|En ce moment, Mila va vers la porte.
+narrateur|La pluie tape le bois.
+narrateur|Maman tend le manteau bleu.
+narrateur|Mila glisse les bras dedans.
+narrateur|Le tissu est un peu froid.
+narrateur|Puis il réchauffe les épaules.
+enfant-f|Mes bottes.
+narrateur|Une botte est à l'envers.
+narrateur|La semelle regarde le plafond.
+enfant-f|Elle est drôle.
+maman|On la retourne ensemble ?
+narrateur|Mila tire la botte.
+narrateur|Maman aide un peu.
+narrateur|La botte redevient une botte.
+enfant-f|L'autre maintenant.
+narrateur|L'autre botte est déjà droite.
+narrateur|Mila enfile les deux.
+narrateur|Ses pieds sont au chaud.
+maman|Prête pour la flaque ?
+enfant-f|Oui !
+narrateur|Elles ouvrent la porte.
+narrateur|L'air sent la terre mouillée.
+narrateur|La flaque brille comme un miroir.
+narrateur|Mila pose un pied.
+narrateur|Ploc.
+narrateur|Puis l'autre pied.
+narrateur|L'eau saute sur le manteau.
+enfant-f|Elle est froide !
+maman|Tes pieds restent au sec ?
+enfant-f|Oui, maman.
+maman|Merci.
+maman|Tu as retourné la botte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1341,12 +1394,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Il pleut. Que met Kenzo ?</t>
+          <t>Il pleut dans le jardin. Que met Mila ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Il pleut. Que met Kenzo ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Il pleut dans le jardin. Que met Mila ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1376,7 +1429,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il met les bottes. Que met Kenzo s'il pleut ?</t>
+          <t>Il met les bottes. Que met Mila s'il pleut ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1425,7 +1478,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1497,10 +1550,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Il pleut. Que met Kenzo ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Il pleut dans le jardin.
+narrateur|Que met Mila ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1525,12 +1578,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a mis le manteau. Il a mis les bottes. Maman était là.</t>
+          <t>Mila reste dans la flaque. Une feuille tourne sur l'eau. Un bateau ! Tu le pousses ? Mila pousse la feuille. Elle va jusqu'au bord. Le cerisier goutte sur le manteau. Toc toc. Le cerisier parle. Il est plein d'eau. Mila fait un autre ploc. L'eau fait des ronds. Le miroir se casse, puis revient. Encore ! Tu vois tes pieds ? Ils sont jaunes, en dessous. Les bottes brillent sous l'eau. Encore un, puis on rentre ? Mila saute tout petit. Un oiseau s'enfuit du cerisier. Ses pieds restent au sec. Le manteau bleu est mouillé dehors. Dedans, Mila a chaud. Une goutte coule jusqu'au nez. Elle chatouille.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Kenzo a mis le manteau. Il a mis les bottes. Maman était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila reste dans la flaque. Une feuille tourne sur l'eau. Un bateau ! Tu le pousses ? Mila pousse la feuille. Elle va jusqu'au bord. Le cerisier goutte sur le manteau. Toc toc. Le cerisier parle. Il est plein d'eau. Mila fait un autre ploc. L'eau fait des ronds. Le miroir se casse, puis revient. Encore ! Tu vois tes pieds ? Ils sont jaunes, en dessous. Les bottes brillent sous l'eau. Encore un, puis on rentre ? Mila saute tout petit. Un oiseau s'enfuit du cerisier. Ses pieds restent au sec. Le manteau bleu est mouillé dehors. Dedans, Mila a chaud. Une goutte coule jusqu'au nez. Elle chatouille.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1586,14 +1639,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1718,33 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a mis le manteau. Il a mis les bottes. Maman était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila reste dans la flaque.
+narrateur|Une feuille tourne sur l'eau.
+enfant-f|Un bateau !
+maman|Tu le pousses ?
+narrateur|Mila pousse la feuille.
+narrateur|Elle va jusqu'au bord.
+narrateur|Le cerisier goutte sur le manteau.
+narrateur|Toc toc.
+enfant-f|Le cerisier parle.
+maman|Il est plein d'eau.
+narrateur|Mila fait un autre ploc.
+narrateur|L'eau fait des ronds.
+narrateur|Le miroir se casse, puis revient.
+enfant-f|Encore !
+maman|Tu vois tes pieds ?
+enfant-f|Ils sont jaunes, en dessous.
+narrateur|Les bottes brillent sous l'eau.
+maman|Encore un, puis on rentre ?
+narrateur|Mila saute tout petit.
+narrateur|Un oiseau s'enfuit du cerisier.
+narrateur|Ses pieds restent au sec.
+narrateur|Le manteau bleu est mouillé dehors.
+narrateur|Dedans, Mila a chaud.
+narrateur|Une goutte coule jusqu'au nez.
+enfant-f|Elle chatouille.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1693,12 +1769,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Kenzo entend la pluie. Ses pieds restent au sec.</t>
+          <t>Elles rentrent. Le cacao est encore tiède. On pose les bottes ? Près de la porte. Mila les aligne. Elles sont mouillées, droites. Plus à l'envers. Le manteau goutte sur le crochet. Mila souffle sur sa tasse. La vapeur lui chatouille le nez.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Kenzo entend la &lt;emphasis level="moderate"&gt;pluie&lt;/emphasis&gt;. Ses pieds restent au sec.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Elles rentrent. Le cacao est encore tiède. On pose les bottes ? Près de la porte. Mila les aligne. Elles sont mouillées, droites. Plus à l'envers. Le manteau goutte sur le crochet. Mila souffle sur sa tasse. La vapeur lui chatouille le nez.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1754,14 +1830,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1833,10 +1909,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo entend la pluie. Ses pieds restent au sec.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Elles rentrent.
+narrateur|Le cacao est encore tiède.
+maman|On pose les bottes ?
+enfant-f|Près de la porte.
+narrateur|Mila les aligne.
+narrateur|Elles sont mouillées, droites.
+narrateur|Plus à l'envers.
+narrateur|Le manteau goutte sur le crochet.
+narrateur|Mila souffle sur sa tasse.
+narrateur|La vapeur lui chatouille le nez.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1861,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Dehors, la flaque brille encore. La feuille bateau attend au bord. Ma flaque. Oui. Les gouttes courent toujours sur la vitre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Dehors, la flaque brille encore. La feuille bateau attend au bord. Ma flaque. Oui. Les gouttes courent toujours sur la vitre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1922,14 +2006,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2001,10 +2085,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Dehors, la flaque brille encore.
+narrateur|La feuille bateau attend au bord.
+enfant-f|Ma flaque.
+maman|Oui.
+narrateur|Les gouttes courent toujours sur la vitre.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2061,6 +2148,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MET.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>entrée de la maison</t>
+          <t>maison puis jardin sous la pluie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kenzo, maman</t>
+          <t>Mila, maman</t>
         </is>
       </c>
     </row>
